--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14D1941-D431-4A22-949D-63ED74C069F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20A08D4-A708-4D63-8B6A-01606CC827B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$328</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$327</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="374">
   <si>
     <t>ID_META</t>
   </si>
@@ -1216,9 +1216,6 @@
   </si>
   <si>
     <t>M00325</t>
-  </si>
-  <si>
-    <t>M00326</t>
   </si>
   <si>
     <t>M00327</t>
@@ -1498,8 +1495,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A94C55CA-EA62-4689-9D49-11D174A7C6C9}" name="Tabla1" displayName="Tabla1" ref="C1:J328" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="C1:J328" xr:uid="{A94C55CA-EA62-4689-9D49-11D174A7C6C9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A94C55CA-EA62-4689-9D49-11D174A7C6C9}" name="Tabla1" displayName="Tabla1" ref="C1:J327" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="C1:J327" xr:uid="{A94C55CA-EA62-4689-9D49-11D174A7C6C9}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="CdD-FEST"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="2">
+      <filters>
+        <filter val="LITA CASTILLO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{762B2E27-3995-4311-9C01-127F54E0F93A}" name="MES" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{1456C7DD-C371-4A0D-84AA-97597FFDA208}" name="PROGRAMA" dataDxfId="6"/>
@@ -1826,7 +1834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J328"/>
+  <dimension ref="A1:J327"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -1873,7 +1881,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -1906,7 +1914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1939,7 +1947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -1972,7 +1980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -2005,7 +2013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -2038,7 +2046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -2071,7 +2079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -2104,7 +2112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -2137,7 +2145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -2170,7 +2178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -2203,7 +2211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -2236,7 +2244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
@@ -2269,7 +2277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
@@ -2302,7 +2310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
@@ -2335,7 +2343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
@@ -2368,7 +2376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
@@ -2401,7 +2409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -2434,7 +2442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
@@ -2467,7 +2475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -2500,7 +2508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
@@ -2533,7 +2541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>29</v>
       </c>
@@ -2566,7 +2574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>30</v>
       </c>
@@ -2599,7 +2607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>31</v>
       </c>
@@ -2632,7 +2640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>32</v>
       </c>
@@ -2665,7 +2673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>33</v>
       </c>
@@ -2698,7 +2706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
@@ -2731,7 +2739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>35</v>
       </c>
@@ -2764,7 +2772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>36</v>
       </c>
@@ -2797,7 +2805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
@@ -2830,7 +2838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>38</v>
       </c>
@@ -2863,7 +2871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>39</v>
       </c>
@@ -2896,7 +2904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>40</v>
       </c>
@@ -2929,7 +2937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>41</v>
       </c>
@@ -2962,7 +2970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>42</v>
       </c>
@@ -2995,7 +3003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>43</v>
       </c>
@@ -3028,7 +3036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>44</v>
       </c>
@@ -3061,7 +3069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>45</v>
       </c>
@@ -3094,7 +3102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>46</v>
       </c>
@@ -3127,7 +3135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>47</v>
       </c>
@@ -3160,7 +3168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>48</v>
       </c>
@@ -3193,7 +3201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>49</v>
       </c>
@@ -3226,7 +3234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>50</v>
       </c>
@@ -3259,7 +3267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>51</v>
       </c>
@@ -3292,7 +3300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>52</v>
       </c>
@@ -3325,7 +3333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>53</v>
       </c>
@@ -3358,7 +3366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>54</v>
       </c>
@@ -3391,7 +3399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>55</v>
       </c>
@@ -3424,7 +3432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>56</v>
       </c>
@@ -3457,7 +3465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>57</v>
       </c>
@@ -3490,7 +3498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>58</v>
       </c>
@@ -3523,7 +3531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>59</v>
       </c>
@@ -3556,7 +3564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>60</v>
       </c>
@@ -3589,7 +3597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>61</v>
       </c>
@@ -3622,7 +3630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>62</v>
       </c>
@@ -3655,7 +3663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>63</v>
       </c>
@@ -3688,7 +3696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>64</v>
       </c>
@@ -3721,7 +3729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>65</v>
       </c>
@@ -3754,7 +3762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>66</v>
       </c>
@@ -3787,7 +3795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>67</v>
       </c>
@@ -3820,7 +3828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>68</v>
       </c>
@@ -3853,7 +3861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>69</v>
       </c>
@@ -3886,7 +3894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>70</v>
       </c>
@@ -3919,7 +3927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>71</v>
       </c>
@@ -3952,7 +3960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>72</v>
       </c>
@@ -3985,7 +3993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>73</v>
       </c>
@@ -4018,7 +4026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>74</v>
       </c>
@@ -4051,7 +4059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>75</v>
       </c>
@@ -4084,7 +4092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>76</v>
       </c>
@@ -4117,7 +4125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>77</v>
       </c>
@@ -4150,7 +4158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>78</v>
       </c>
@@ -4183,7 +4191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>79</v>
       </c>
@@ -4216,7 +4224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>80</v>
       </c>
@@ -4249,7 +4257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>81</v>
       </c>
@@ -4282,7 +4290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>82</v>
       </c>
@@ -4315,7 +4323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>83</v>
       </c>
@@ -4348,7 +4356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>84</v>
       </c>
@@ -4381,7 +4389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>85</v>
       </c>
@@ -4414,7 +4422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>86</v>
       </c>
@@ -4447,7 +4455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>87</v>
       </c>
@@ -4480,7 +4488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>88</v>
       </c>
@@ -4513,7 +4521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>89</v>
       </c>
@@ -4546,7 +4554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>90</v>
       </c>
@@ -4579,7 +4587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>91</v>
       </c>
@@ -4612,7 +4620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>92</v>
       </c>
@@ -4645,7 +4653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>93</v>
       </c>
@@ -4678,7 +4686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>94</v>
       </c>
@@ -4711,7 +4719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>95</v>
       </c>
@@ -4744,7 +4752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>96</v>
       </c>
@@ -4777,7 +4785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>97</v>
       </c>
@@ -4810,7 +4818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>98</v>
       </c>
@@ -4843,7 +4851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>99</v>
       </c>
@@ -4876,7 +4884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>100</v>
       </c>
@@ -4909,7 +4917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>101</v>
       </c>
@@ -4942,7 +4950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>102</v>
       </c>
@@ -4975,7 +4983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>103</v>
       </c>
@@ -5008,7 +5016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>104</v>
       </c>
@@ -5041,7 +5049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>105</v>
       </c>
@@ -5074,7 +5082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>106</v>
       </c>
@@ -5107,7 +5115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>107</v>
       </c>
@@ -5140,7 +5148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>108</v>
       </c>
@@ -5173,7 +5181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>109</v>
       </c>
@@ -5206,7 +5214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>110</v>
       </c>
@@ -5239,7 +5247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>111</v>
       </c>
@@ -5272,7 +5280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>112</v>
       </c>
@@ -5305,7 +5313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>113</v>
       </c>
@@ -5338,7 +5346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>114</v>
       </c>
@@ -5371,7 +5379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>115</v>
       </c>
@@ -5404,7 +5412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>116</v>
       </c>
@@ -5437,7 +5445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>117</v>
       </c>
@@ -5470,7 +5478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>118</v>
       </c>
@@ -5503,7 +5511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>119</v>
       </c>
@@ -5536,7 +5544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>120</v>
       </c>
@@ -5569,7 +5577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>121</v>
       </c>
@@ -5602,7 +5610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>122</v>
       </c>
@@ -5635,7 +5643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>123</v>
       </c>
@@ -5668,7 +5676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>124</v>
       </c>
@@ -5701,7 +5709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>125</v>
       </c>
@@ -5734,7 +5742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>126</v>
       </c>
@@ -5767,7 +5775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>127</v>
       </c>
@@ -5800,7 +5808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>128</v>
       </c>
@@ -5833,7 +5841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>129</v>
       </c>
@@ -5866,7 +5874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>130</v>
       </c>
@@ -5899,7 +5907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>131</v>
       </c>
@@ -5932,7 +5940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>132</v>
       </c>
@@ -5965,7 +5973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>133</v>
       </c>
@@ -5998,7 +6006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>134</v>
       </c>
@@ -6031,7 +6039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>135</v>
       </c>
@@ -6064,7 +6072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>136</v>
       </c>
@@ -6097,7 +6105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>137</v>
       </c>
@@ -6130,7 +6138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>138</v>
       </c>
@@ -6163,7 +6171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>139</v>
       </c>
@@ -6196,7 +6204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>140</v>
       </c>
@@ -6229,7 +6237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>141</v>
       </c>
@@ -6262,7 +6270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>142</v>
       </c>
@@ -6295,7 +6303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>143</v>
       </c>
@@ -6328,7 +6336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>144</v>
       </c>
@@ -6361,7 +6369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>145</v>
       </c>
@@ -6394,7 +6402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>146</v>
       </c>
@@ -6427,7 +6435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>147</v>
       </c>
@@ -6460,7 +6468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>148</v>
       </c>
@@ -6493,7 +6501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>149</v>
       </c>
@@ -6526,7 +6534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>150</v>
       </c>
@@ -6559,7 +6567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>151</v>
       </c>
@@ -6592,7 +6600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>152</v>
       </c>
@@ -6625,7 +6633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>153</v>
       </c>
@@ -6658,7 +6666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>154</v>
       </c>
@@ -6691,7 +6699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>155</v>
       </c>
@@ -6724,7 +6732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>156</v>
       </c>
@@ -6757,7 +6765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>157</v>
       </c>
@@ -6790,7 +6798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>158</v>
       </c>
@@ -6823,7 +6831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>159</v>
       </c>
@@ -6856,7 +6864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>357</v>
       </c>
@@ -6889,7 +6897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>160</v>
       </c>
@@ -6922,7 +6930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>161</v>
       </c>
@@ -6955,7 +6963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>162</v>
       </c>
@@ -6988,7 +6996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>163</v>
       </c>
@@ -7021,7 +7029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>164</v>
       </c>
@@ -7054,7 +7062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>165</v>
       </c>
@@ -7087,7 +7095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>166</v>
       </c>
@@ -7120,7 +7128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>167</v>
       </c>
@@ -7153,7 +7161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>168</v>
       </c>
@@ -7186,7 +7194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>169</v>
       </c>
@@ -7219,7 +7227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>170</v>
       </c>
@@ -7252,7 +7260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>171</v>
       </c>
@@ -7285,7 +7293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>172</v>
       </c>
@@ -7318,7 +7326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>173</v>
       </c>
@@ -7351,7 +7359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>174</v>
       </c>
@@ -7384,7 +7392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>175</v>
       </c>
@@ -7417,7 +7425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>176</v>
       </c>
@@ -7450,7 +7458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>177</v>
       </c>
@@ -7483,7 +7491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>178</v>
       </c>
@@ -7516,7 +7524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>179</v>
       </c>
@@ -7549,7 +7557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>180</v>
       </c>
@@ -7582,7 +7590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>181</v>
       </c>
@@ -7615,7 +7623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>182</v>
       </c>
@@ -7648,7 +7656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>183</v>
       </c>
@@ -7681,7 +7689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>184</v>
       </c>
@@ -7714,7 +7722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>185</v>
       </c>
@@ -7747,7 +7755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>186</v>
       </c>
@@ -7780,7 +7788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>187</v>
       </c>
@@ -7813,7 +7821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>188</v>
       </c>
@@ -7846,7 +7854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>189</v>
       </c>
@@ -7879,7 +7887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>190</v>
       </c>
@@ -7912,7 +7920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>191</v>
       </c>
@@ -7945,7 +7953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>192</v>
       </c>
@@ -7978,7 +7986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>193</v>
       </c>
@@ -8011,7 +8019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>194</v>
       </c>
@@ -8044,7 +8052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>195</v>
       </c>
@@ -8077,7 +8085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>196</v>
       </c>
@@ -8110,7 +8118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>197</v>
       </c>
@@ -8143,7 +8151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>198</v>
       </c>
@@ -8176,7 +8184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>199</v>
       </c>
@@ -8209,7 +8217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>200</v>
       </c>
@@ -8242,7 +8250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>201</v>
       </c>
@@ -8275,7 +8283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>358</v>
       </c>
@@ -8308,7 +8316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>202</v>
       </c>
@@ -8341,7 +8349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>203</v>
       </c>
@@ -8374,7 +8382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>204</v>
       </c>
@@ -8407,7 +8415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>205</v>
       </c>
@@ -8440,7 +8448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>206</v>
       </c>
@@ -8473,7 +8481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>207</v>
       </c>
@@ -8506,7 +8514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>208</v>
       </c>
@@ -8539,7 +8547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>209</v>
       </c>
@@ -8572,7 +8580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>210</v>
       </c>
@@ -8605,7 +8613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>211</v>
       </c>
@@ -8638,7 +8646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>212</v>
       </c>
@@ -8671,7 +8679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>213</v>
       </c>
@@ -8704,7 +8712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>214</v>
       </c>
@@ -8737,7 +8745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>215</v>
       </c>
@@ -8770,7 +8778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>216</v>
       </c>
@@ -8803,7 +8811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>217</v>
       </c>
@@ -8836,7 +8844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>218</v>
       </c>
@@ -8869,7 +8877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>219</v>
       </c>
@@ -8902,7 +8910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>220</v>
       </c>
@@ -8935,7 +8943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>221</v>
       </c>
@@ -8968,7 +8976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>222</v>
       </c>
@@ -9001,7 +9009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>253</v>
       </c>
@@ -9034,7 +9042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>254</v>
       </c>
@@ -9067,7 +9075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>255</v>
       </c>
@@ -9199,7 +9207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>259</v>
       </c>
@@ -9229,7 +9237,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>260</v>
       </c>
@@ -9262,7 +9270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>261</v>
       </c>
@@ -9295,7 +9303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>262</v>
       </c>
@@ -9328,7 +9336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>263</v>
       </c>
@@ -9361,7 +9369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>264</v>
       </c>
@@ -9394,7 +9402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>265</v>
       </c>
@@ -9427,7 +9435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>266</v>
       </c>
@@ -9460,7 +9468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>267</v>
       </c>
@@ -9493,7 +9501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>268</v>
       </c>
@@ -9526,7 +9534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>269</v>
       </c>
@@ -9559,7 +9567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>270</v>
       </c>
@@ -9592,7 +9600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>271</v>
       </c>
@@ -9625,7 +9633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>272</v>
       </c>
@@ -9658,7 +9666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>273</v>
       </c>
@@ -9691,7 +9699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>274</v>
       </c>
@@ -9724,7 +9732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>275</v>
       </c>
@@ -9757,7 +9765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>276</v>
       </c>
@@ -9790,7 +9798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>277</v>
       </c>
@@ -9823,7 +9831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>278</v>
       </c>
@@ -9856,7 +9864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>279</v>
       </c>
@@ -9889,7 +9897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>280</v>
       </c>
@@ -9922,7 +9930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>281</v>
       </c>
@@ -9955,7 +9963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>282</v>
       </c>
@@ -9988,7 +9996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>283</v>
       </c>
@@ -10021,7 +10029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>284</v>
       </c>
@@ -10054,7 +10062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>285</v>
       </c>
@@ -10087,7 +10095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>286</v>
       </c>
@@ -10120,7 +10128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>287</v>
       </c>
@@ -10153,7 +10161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>288</v>
       </c>
@@ -10186,7 +10194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>289</v>
       </c>
@@ -10219,7 +10227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>290</v>
       </c>
@@ -10252,7 +10260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>291</v>
       </c>
@@ -10285,7 +10293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>292</v>
       </c>
@@ -10318,7 +10326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>293</v>
       </c>
@@ -10351,7 +10359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>294</v>
       </c>
@@ -10384,7 +10392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>295</v>
       </c>
@@ -10417,7 +10425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>296</v>
       </c>
@@ -10450,7 +10458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>297</v>
       </c>
@@ -10483,7 +10491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>298</v>
       </c>
@@ -10516,7 +10524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>299</v>
       </c>
@@ -10549,7 +10557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>300</v>
       </c>
@@ -10582,7 +10590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>301</v>
       </c>
@@ -10615,7 +10623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>302</v>
       </c>
@@ -10648,7 +10656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>303</v>
       </c>
@@ -10681,7 +10689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>304</v>
       </c>
@@ -10714,7 +10722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>305</v>
       </c>
@@ -10747,7 +10755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>306</v>
       </c>
@@ -10780,7 +10788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>307</v>
       </c>
@@ -10813,7 +10821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>308</v>
       </c>
@@ -10846,7 +10854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>309</v>
       </c>
@@ -10879,7 +10887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>310</v>
       </c>
@@ -10912,7 +10920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>311</v>
       </c>
@@ -10945,7 +10953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>312</v>
       </c>
@@ -10978,7 +10986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>313</v>
       </c>
@@ -11011,7 +11019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>314</v>
       </c>
@@ -11044,7 +11052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>315</v>
       </c>
@@ -11077,7 +11085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>316</v>
       </c>
@@ -11110,7 +11118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>317</v>
       </c>
@@ -11143,7 +11151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>318</v>
       </c>
@@ -11176,7 +11184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>319</v>
       </c>
@@ -11209,7 +11217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>320</v>
       </c>
@@ -11242,7 +11250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>321</v>
       </c>
@@ -11275,7 +11283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>322</v>
       </c>
@@ -11308,7 +11316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>323</v>
       </c>
@@ -11341,7 +11349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>324</v>
       </c>
@@ -11374,7 +11382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>325</v>
       </c>
@@ -11407,7 +11415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>326</v>
       </c>
@@ -11440,7 +11448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>327</v>
       </c>
@@ -11473,7 +11481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>328</v>
       </c>
@@ -11506,7 +11514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>329</v>
       </c>
@@ -11539,7 +11547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>330</v>
       </c>
@@ -11572,7 +11580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>331</v>
       </c>
@@ -11605,7 +11613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>332</v>
       </c>
@@ -11638,7 +11646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>333</v>
       </c>
@@ -11671,7 +11679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>334</v>
       </c>
@@ -11704,7 +11712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>335</v>
       </c>
@@ -11737,7 +11745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>336</v>
       </c>
@@ -11770,7 +11778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>337</v>
       </c>
@@ -11803,7 +11811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>338</v>
       </c>
@@ -11836,7 +11844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>339</v>
       </c>
@@ -11869,7 +11877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>340</v>
       </c>
@@ -11902,7 +11910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>341</v>
       </c>
@@ -11935,7 +11943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>342</v>
       </c>
@@ -11968,7 +11976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>343</v>
       </c>
@@ -12001,7 +12009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>344</v>
       </c>
@@ -12067,7 +12075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>346</v>
       </c>
@@ -12100,7 +12108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>347</v>
       </c>
@@ -12133,7 +12141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>359</v>
       </c>
@@ -12166,7 +12174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>360</v>
       </c>
@@ -12226,13 +12234,13 @@
         <v>230</v>
       </c>
       <c r="I315" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J315" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>362</v>
       </c>
@@ -12265,7 +12273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>363</v>
       </c>
@@ -12298,7 +12306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>364</v>
       </c>
@@ -12358,13 +12366,13 @@
         <v>230</v>
       </c>
       <c r="I319" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J319" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>366</v>
       </c>
@@ -12397,7 +12405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>367</v>
       </c>
@@ -12430,7 +12438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>368</v>
       </c>
@@ -12463,7 +12471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>369</v>
       </c>
@@ -12523,7 +12531,7 @@
         <v>230</v>
       </c>
       <c r="I324" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J324" s="1">
         <v>0</v>
@@ -12556,7 +12564,7 @@
         <v>230</v>
       </c>
       <c r="I325" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J325" s="1">
         <v>0</v>
@@ -12595,69 +12603,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B327" s="1">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C327" s="1">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D327" s="1" t="s">
         <v>252</v>
       </c>
       <c r="E327" s="1" t="str">
         <f ca="1">+UPPER(Tabla1[[#This Row],[ESPECIALISTA]])</f>
-        <v>LITA CASTILLO</v>
+        <v>MIRIAM PARI</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G327" s="1" t="s">
         <v>355</v>
       </c>
       <c r="H327" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I327" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J327" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A328" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="B328" s="1">
-        <v>2026</v>
-      </c>
-      <c r="C328" s="1">
-        <v>12</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E328" s="1" t="str">
-        <f ca="1">+UPPER(Tabla1[[#This Row],[ESPECIALISTA]])</f>
-        <v>MIRIAM PARI</v>
-      </c>
-      <c r="F328" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="G328" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="H328" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="I328" s="1">
-        <v>10</v>
-      </c>
-      <c r="J328" s="1">
         <v>0</v>
       </c>
     </row>
